--- a/Excel/Language/#genFromCode.xlsx
+++ b/Excel/Language/#genFromCode.xlsx
@@ -1,18 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\UnityWork\Excel\Language\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="26325" windowHeight="10830"/>
+    <workbookView windowWidth="27105" windowHeight="12945"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures">
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
     <r>
       <rPr>
@@ -35,47 +40,38 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">key</t>
+      <t>key</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">中文</t>
+    <t>函数调用区域显示</t>
   </si>
   <si>
-    <t xml:space="preserve">英语</t>
+    <t>英语</t>
   </si>
   <si>
-    <t xml:space="preserve">Chinese</t>
+    <t>English</t>
   </si>
   <si>
-    <t xml:space="preserve">English</t>
+    <t>a</t>
   </si>
   <si>
-    <t xml:space="preserve">a</t>
+    <t/>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t>b</t>
   </si>
   <si>
-    <t xml:space="preserve">b</t>
+    <t>卢卡斯的积分</t>
   </si>
   <si>
-    <t xml:space="preserve">卢卡斯的积分</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Program[MoveNext]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">劳动节快乐感觉</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC_LanguageChange[.ctor]</t>
+    <t>劳动节快乐感觉</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -91,7 +87,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
@@ -99,7 +95,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
@@ -751,8 +747,8 @@
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -981,7 +977,7 @@
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
-          <a:sp3d prstMaterial="warmMatte">
+          <a:sp3d>
             <a:bevelT w="63500" h="25400"/>
           </a:sp3d>
         </a:effectStyle>
@@ -1043,70 +1039,68 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="28.875" customWidth="1"/>
     <col min="2" max="2" width="27.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12" customHeight="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" ht="12" customHeight="1" spans="1:3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="0" t="s">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>5</v>
+      <c r="C3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>7</v>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>6</v>
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>6</v>
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
